--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_shop/lang_shop__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_shop/lang_shop__ui__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Cửa hàng Vũ khí</t>
+          <t>Dòng Vũ Khí</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Cửa hàng Dược Phẩm</t>
+          <t>Cửa Hàng Dược Phẩm</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Cửa hàng "Đồ Lưu niệm"</t>
+          <t>"Cửa Hàng" Kỷ Vật</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Interference Exchange</t>
+          <t>Trao Đổi Nhiễu Loạn</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Ma Anh ấy's Grocers</t>
+          <t>Cửa Hàng Tạp Hóa Ma He</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Panhua's Kitchen</t>
+          <t>Bếp Nhà Panhua</t>
         </is>
       </c>
     </row>
